--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09F5E29-C534-4359-AB7B-E5449C61A1AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38836A4-DF96-49EC-9068-D8B8501999F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="116">
   <si>
     <t>Date</t>
   </si>
@@ -365,6 +365,30 @@
   </si>
   <si>
     <t>input search filter</t>
+  </si>
+  <si>
+    <t>react big calendar</t>
+  </si>
+  <si>
+    <t>basic setup and configuration</t>
+  </si>
+  <si>
+    <t>date-fns</t>
+  </si>
+  <si>
+    <t>date fns docs</t>
+  </si>
+  <si>
+    <t>basic functions</t>
+  </si>
+  <si>
+    <t>react-big-calendar localiser</t>
+  </si>
+  <si>
+    <t>localsiser functions for startofWeek</t>
+  </si>
+  <si>
+    <t>start of week format</t>
   </si>
 </sst>
 </file>
@@ -776,7 +800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90D4E2F-31CB-4504-B764-69927272A7DB}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -1211,6 +1235,48 @@
       </c>
       <c r="D32" s="3" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>45993</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>45996</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>45996</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1246,9 +1312,12 @@
     <hyperlink ref="C30" r:id="rId28" xr:uid="{5A1495FF-2FD8-48B3-A242-89BA4C559C98}"/>
     <hyperlink ref="C32" r:id="rId29" xr:uid="{F1C3C78B-B8E6-48A4-8F51-5148F47AE238}"/>
     <hyperlink ref="C31" r:id="rId30" xr:uid="{7D53FE41-D04E-4CFD-855A-40B65B7655E2}"/>
+    <hyperlink ref="C33" r:id="rId31" xr:uid="{254DFCB9-A620-4255-A697-2CB786CA7CE3}"/>
+    <hyperlink ref="C34" r:id="rId32" xr:uid="{9199EC49-22AB-4322-AC33-4F2E57753EE3}"/>
+    <hyperlink ref="C35" r:id="rId33" xr:uid="{01609D78-3D3A-47F8-BF5A-5FF917290433}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId34"/>
 </worksheet>
 </file>
 

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38836A4-DF96-49EC-9068-D8B8501999F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D987F59F-8DD2-4532-81DA-6CA30C4D2FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="121">
   <si>
     <t>Date</t>
   </si>
@@ -389,6 +389,21 @@
   </si>
   <si>
     <t>start of week format</t>
+  </si>
+  <si>
+    <t>react-big-calendar</t>
+  </si>
+  <si>
+    <t>onSeclectEvent</t>
+  </si>
+  <si>
+    <t>Calendar's onSelectEvent</t>
+  </si>
+  <si>
+    <t>calendar setup and localiser</t>
+  </si>
+  <si>
+    <t>starting code for calendar and localiser</t>
   </si>
 </sst>
 </file>
@@ -800,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90D4E2F-31CB-4504-B764-69927272A7DB}">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -1253,16 +1268,16 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>45996</v>
+        <v>45993</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1270,13 +1285,41 @@
         <v>45996</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>45996</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C36" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>45998</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1313,11 +1356,13 @@
     <hyperlink ref="C32" r:id="rId29" xr:uid="{F1C3C78B-B8E6-48A4-8F51-5148F47AE238}"/>
     <hyperlink ref="C31" r:id="rId30" xr:uid="{7D53FE41-D04E-4CFD-855A-40B65B7655E2}"/>
     <hyperlink ref="C33" r:id="rId31" xr:uid="{254DFCB9-A620-4255-A697-2CB786CA7CE3}"/>
-    <hyperlink ref="C34" r:id="rId32" xr:uid="{9199EC49-22AB-4322-AC33-4F2E57753EE3}"/>
-    <hyperlink ref="C35" r:id="rId33" xr:uid="{01609D78-3D3A-47F8-BF5A-5FF917290433}"/>
+    <hyperlink ref="C35" r:id="rId32" xr:uid="{9199EC49-22AB-4322-AC33-4F2E57753EE3}"/>
+    <hyperlink ref="C36" r:id="rId33" xr:uid="{01609D78-3D3A-47F8-BF5A-5FF917290433}"/>
+    <hyperlink ref="C37" r:id="rId34" xr:uid="{3606DB42-0C27-49DA-ACF9-27FB2D79623A}"/>
+    <hyperlink ref="C34" r:id="rId35" xr:uid="{255A3E96-C2D8-4932-B7F1-72D2BB7D9B98}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId34"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId36"/>
 </worksheet>
 </file>
 

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D987F59F-8DD2-4532-81DA-6CA30C4D2FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C791BAAD-B5AD-428C-ADCE-7A71EB81A0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="127">
   <si>
     <t>Date</t>
   </si>
@@ -404,6 +404,24 @@
   </si>
   <si>
     <t>starting code for calendar and localiser</t>
+  </si>
+  <si>
+    <t>eventPropGetter</t>
+  </si>
+  <si>
+    <t>custom styling of Calendar events</t>
+  </si>
+  <si>
+    <t>toLocaleDateString()</t>
+  </si>
+  <si>
+    <t>mdn docs</t>
+  </si>
+  <si>
+    <t>method usage</t>
+  </si>
+  <si>
+    <t>toLocaleTimeString()</t>
   </si>
 </sst>
 </file>
@@ -815,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90D4E2F-31CB-4504-B764-69927272A7DB}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -1320,6 +1338,48 @@
       </c>
       <c r="D37" s="3" t="s">
         <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
+        <v>45998</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>45999</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <v>45999</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1360,9 +1420,12 @@
     <hyperlink ref="C36" r:id="rId33" xr:uid="{01609D78-3D3A-47F8-BF5A-5FF917290433}"/>
     <hyperlink ref="C37" r:id="rId34" xr:uid="{3606DB42-0C27-49DA-ACF9-27FB2D79623A}"/>
     <hyperlink ref="C34" r:id="rId35" xr:uid="{255A3E96-C2D8-4932-B7F1-72D2BB7D9B98}"/>
+    <hyperlink ref="C38" r:id="rId36" xr:uid="{0547D2F1-2A1F-4CE3-86EF-58E23F51E94A}"/>
+    <hyperlink ref="C39" r:id="rId37" xr:uid="{A68626F7-6347-4DAC-B7E4-420C7B476A2F}"/>
+    <hyperlink ref="C40" r:id="rId38" xr:uid="{CB9BD13E-9B50-44C5-82C4-024640EDF863}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId36"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId39"/>
 </worksheet>
 </file>
 

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C791BAAD-B5AD-428C-ADCE-7A71EB81A0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D8F3D7-FFDF-49C2-A2AF-44D8415290A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -833,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90D4E2F-31CB-4504-B764-69927272A7DB}">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -1381,6 +1381,10 @@
       <c r="D40" s="3" t="s">
         <v>125</v>
       </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="5"/>
+      <c r="C41" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D8F3D7-FFDF-49C2-A2AF-44D8415290A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4082E4B-0927-4BCE-B21A-9F017BB3E267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="130">
   <si>
     <t>Date</t>
   </si>
@@ -422,6 +422,15 @@
   </si>
   <si>
     <t>toLocaleTimeString()</t>
+  </si>
+  <si>
+    <t>postgres interval</t>
+  </si>
+  <si>
+    <t>postgres tutorial</t>
+  </si>
+  <si>
+    <t>interval function</t>
   </si>
 </sst>
 </file>
@@ -1383,8 +1392,18 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="C41" s="6"/>
+      <c r="A41" s="5">
+        <v>46033</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>129</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1427,9 +1446,10 @@
     <hyperlink ref="C38" r:id="rId36" xr:uid="{0547D2F1-2A1F-4CE3-86EF-58E23F51E94A}"/>
     <hyperlink ref="C39" r:id="rId37" xr:uid="{A68626F7-6347-4DAC-B7E4-420C7B476A2F}"/>
     <hyperlink ref="C40" r:id="rId38" xr:uid="{CB9BD13E-9B50-44C5-82C4-024640EDF863}"/>
+    <hyperlink ref="C41" r:id="rId39" xr:uid="{816ECC41-1389-44F8-9A20-42011A9E6079}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId39"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId40"/>
 </worksheet>
 </file>
 

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4082E4B-0927-4BCE-B21A-9F017BB3E267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD466FB-01E4-4627-B116-4A0F89BC9FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="132">
   <si>
     <t>Date</t>
   </si>
@@ -431,6 +431,12 @@
   </si>
   <si>
     <t>interval function</t>
+  </si>
+  <si>
+    <t>socket io</t>
+  </si>
+  <si>
+    <t>socket io article</t>
   </si>
 </sst>
 </file>
@@ -842,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90D4E2F-31CB-4504-B764-69927272A7DB}">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -1403,6 +1409,17 @@
       </c>
       <c r="D41" s="3" t="s">
         <v>129</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>45677</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1447,9 +1464,10 @@
     <hyperlink ref="C39" r:id="rId37" xr:uid="{A68626F7-6347-4DAC-B7E4-420C7B476A2F}"/>
     <hyperlink ref="C40" r:id="rId38" xr:uid="{CB9BD13E-9B50-44C5-82C4-024640EDF863}"/>
     <hyperlink ref="C41" r:id="rId39" xr:uid="{816ECC41-1389-44F8-9A20-42011A9E6079}"/>
+    <hyperlink ref="C42" r:id="rId40" xr:uid="{2E2C1DD5-3948-43F7-B7A3-FE0B19F7DEEB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId40"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId41"/>
 </worksheet>
 </file>
 

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD466FB-01E4-4627-B116-4A0F89BC9FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903368B1-2000-4267-B6A4-E9A67AE6C956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="143">
   <si>
     <t>Date</t>
   </si>
@@ -437,6 +437,39 @@
   </si>
   <si>
     <t>socket io article</t>
+  </si>
+  <si>
+    <t>socket.io with react</t>
+  </si>
+  <si>
+    <t>talks about the socket.io frontend setting option of transports: ["websockets"]</t>
+  </si>
+  <si>
+    <t>socket.io official docs on how to set up on frontend and options to use</t>
+  </si>
+  <si>
+    <t>websocket video</t>
+  </si>
+  <si>
+    <t>socket.io jwt auth</t>
+  </si>
+  <si>
+    <t>socket io jwt auth</t>
+  </si>
+  <si>
+    <t>how to usensocket.io middleware with jwt</t>
+  </si>
+  <si>
+    <t>socket.io clientside auth requirmenets</t>
+  </si>
+  <si>
+    <t>how to send auth info from client to server when attempting websocket signin</t>
+  </si>
+  <si>
+    <t>socket.io clientside options and middleware</t>
+  </si>
+  <si>
+    <t>how to create socket.io middleware and ensure client  sends required auth token</t>
   </si>
 </sst>
 </file>
@@ -848,7 +881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90D4E2F-31CB-4504-B764-69927272A7DB}">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -1420,6 +1453,87 @@
       </c>
       <c r="C42" s="6" t="s">
         <v>131</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <v>46048</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>46053</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>46053</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1465,9 +1579,15 @@
     <hyperlink ref="C40" r:id="rId38" xr:uid="{CB9BD13E-9B50-44C5-82C4-024640EDF863}"/>
     <hyperlink ref="C41" r:id="rId39" xr:uid="{816ECC41-1389-44F8-9A20-42011A9E6079}"/>
     <hyperlink ref="C42" r:id="rId40" xr:uid="{2E2C1DD5-3948-43F7-B7A3-FE0B19F7DEEB}"/>
+    <hyperlink ref="C44" r:id="rId41" xr:uid="{6764F858-515A-4B83-9216-FFBFA8FCE642}"/>
+    <hyperlink ref="C45" r:id="rId42" xr:uid="{6E6DE7E9-364C-4FCC-A5DA-CBB159AD0435}"/>
+    <hyperlink ref="C43" r:id="rId43" xr:uid="{1C315DF0-53A6-45A6-A02F-95EC1F55D663}"/>
+    <hyperlink ref="C46" r:id="rId44" xr:uid="{D1A2AF0B-0CA2-407A-B6B1-EA7B73E18591}"/>
+    <hyperlink ref="C47" r:id="rId45" location="auth" xr:uid="{BC5DCA87-B939-4246-9E7B-C0D371B8B3B4}"/>
+    <hyperlink ref="C48" r:id="rId46" location="sending-credentials" xr:uid="{ABE0F341-2A39-4173-9F0A-66003E4641B7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId41"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId47"/>
 </worksheet>
 </file>
 

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903368B1-2000-4267-B6A4-E9A67AE6C956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143330AB-F02D-4EAA-9AFE-D1794CBD7CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
   <sheets>
     <sheet name="inspriation sources" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="146">
   <si>
     <t>Date</t>
   </si>
@@ -470,6 +470,15 @@
   </si>
   <si>
     <t>how to create socket.io middleware and ensure client  sends required auth token</t>
+  </si>
+  <si>
+    <t>socket.io data</t>
+  </si>
+  <si>
+    <t>adding data to socket object</t>
+  </si>
+  <si>
+    <t>stack overflow shows to use socket.data object to add data</t>
   </si>
 </sst>
 </file>
@@ -881,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90D4E2F-31CB-4504-B764-69927272A7DB}">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -1534,6 +1543,20 @@
       </c>
       <c r="D48" s="3" t="s">
         <v>142</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>46063</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1585,9 +1608,10 @@
     <hyperlink ref="C46" r:id="rId44" xr:uid="{D1A2AF0B-0CA2-407A-B6B1-EA7B73E18591}"/>
     <hyperlink ref="C47" r:id="rId45" location="auth" xr:uid="{BC5DCA87-B939-4246-9E7B-C0D371B8B3B4}"/>
     <hyperlink ref="C48" r:id="rId46" location="sending-credentials" xr:uid="{ABE0F341-2A39-4173-9F0A-66003E4641B7}"/>
+    <hyperlink ref="C49" r:id="rId47" xr:uid="{2E62C5DE-3858-4683-89AA-22F59BF60F30}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId47"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId48"/>
 </worksheet>
 </file>
 

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{143330AB-F02D-4EAA-9AFE-D1794CBD7CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9837EB9-1B91-492E-B5A3-2E2F9CEBA9FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="152">
   <si>
     <t>Date</t>
   </si>
@@ -479,6 +479,24 @@
   </si>
   <si>
     <t>stack overflow shows to use socket.data object to add data</t>
+  </si>
+  <si>
+    <t>postgres upsert</t>
+  </si>
+  <si>
+    <t>used in socket.io to reduce DB searches</t>
+  </si>
+  <si>
+    <t>10-17/2/26</t>
+  </si>
+  <si>
+    <t>socket.io + react webchat</t>
+  </si>
+  <si>
+    <t>webchat</t>
+  </si>
+  <si>
+    <t>codesistency on youtube</t>
   </si>
 </sst>
 </file>
@@ -890,7 +908,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90D4E2F-31CB-4504-B764-69927272A7DB}">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -1557,6 +1575,34 @@
       </c>
       <c r="D49" s="3" t="s">
         <v>145</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>46070</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -1609,9 +1655,11 @@
     <hyperlink ref="C47" r:id="rId45" location="auth" xr:uid="{BC5DCA87-B939-4246-9E7B-C0D371B8B3B4}"/>
     <hyperlink ref="C48" r:id="rId46" location="sending-credentials" xr:uid="{ABE0F341-2A39-4173-9F0A-66003E4641B7}"/>
     <hyperlink ref="C49" r:id="rId47" xr:uid="{2E62C5DE-3858-4683-89AA-22F59BF60F30}"/>
+    <hyperlink ref="C51" r:id="rId48" xr:uid="{F155139A-3434-4782-B615-64B486D351D1}"/>
+    <hyperlink ref="C50" r:id="rId49" xr:uid="{76697DBB-3F51-4C18-B8A6-8E781AB753A0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId48"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId50"/>
 </worksheet>
 </file>
 

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9837EB9-1B91-492E-B5A3-2E2F9CEBA9FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5613477-F297-4AD4-85A7-A87F5B2DA9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
   <sheets>
     <sheet name="inspriation sources" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="155">
   <si>
     <t>Date</t>
   </si>
@@ -497,6 +497,15 @@
   </si>
   <si>
     <t>codesistency on youtube</t>
+  </si>
+  <si>
+    <t>referenced at</t>
+  </si>
+  <si>
+    <t>3.2.1</t>
+  </si>
+  <si>
+    <t>3.2.2</t>
   </si>
 </sst>
 </file>
@@ -908,17 +917,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90D4E2F-31CB-4504-B764-69927272A7DB}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="92.140625" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="89.7109375" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="4"/>
+    <col min="5" max="5" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -931,8 +941,11 @@
       <c r="D1" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>45931</v>
       </c>
@@ -943,7 +956,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>45932</v>
       </c>
@@ -953,8 +966,14 @@
       <c r="C3" s="6" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>45933</v>
       </c>
@@ -964,8 +983,14 @@
       <c r="C4" s="6" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>45934</v>
       </c>
@@ -975,8 +1000,14 @@
       <c r="C5" s="6" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>45935</v>
       </c>
@@ -986,8 +1017,14 @@
       <c r="C6" s="6" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F6" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>45936</v>
       </c>
@@ -997,8 +1034,14 @@
       <c r="C7" s="6" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F7" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>45937</v>
       </c>
@@ -1011,8 +1054,14 @@
       <c r="D8" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="E8" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F8" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>45938</v>
       </c>
@@ -1025,8 +1074,14 @@
       <c r="D9" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E9" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>45939</v>
       </c>
@@ -1039,8 +1094,14 @@
       <c r="D10" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F10" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>45940</v>
       </c>
@@ -1053,8 +1114,14 @@
       <c r="D11" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F11" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>45941</v>
       </c>
@@ -1068,7 +1135,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>45942</v>
       </c>
@@ -1082,7 +1149,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>45943</v>
       </c>
@@ -1096,7 +1163,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>45944</v>
       </c>
@@ -1110,7 +1177,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>45945</v>
       </c>
@@ -1123,8 +1190,14 @@
       <c r="D16" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F16" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>45946</v>
       </c>
@@ -1138,7 +1211,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>45947</v>
       </c>
@@ -1152,7 +1225,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>45948</v>
       </c>
@@ -1166,7 +1239,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>45949</v>
       </c>
@@ -1180,7 +1253,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>45950</v>
       </c>
@@ -1194,7 +1267,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>45951</v>
       </c>
@@ -1208,7 +1281,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>45952</v>
       </c>
@@ -1222,7 +1295,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>45953</v>
       </c>
@@ -1236,7 +1309,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>45954</v>
       </c>
@@ -1250,7 +1323,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>45955</v>
       </c>
@@ -1264,7 +1337,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>45956</v>
       </c>
@@ -1278,7 +1351,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>45957</v>
       </c>
@@ -1291,8 +1364,14 @@
       <c r="D28" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F28" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>45958</v>
       </c>
@@ -1303,7 +1382,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>45963</v>
       </c>
@@ -1317,7 +1396,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>45971</v>
       </c>
@@ -1331,7 +1410,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>45973</v>
       </c>

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5613477-F297-4AD4-85A7-A87F5B2DA9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942E6BCB-826D-4D5A-8E37-C82D4CF9727D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="165">
   <si>
     <t>Date</t>
   </si>
@@ -506,6 +506,36 @@
   </si>
   <si>
     <t>3.2.2</t>
+  </si>
+  <si>
+    <t>3.2.3</t>
+  </si>
+  <si>
+    <t>3.2.4</t>
+  </si>
+  <si>
+    <t>basic walkthrough</t>
+  </si>
+  <si>
+    <t>react</t>
+  </si>
+  <si>
+    <t>anson dev</t>
+  </si>
+  <si>
+    <t>jwt</t>
+  </si>
+  <si>
+    <t>npm docs</t>
+  </si>
+  <si>
+    <t>jwt package functions</t>
+  </si>
+  <si>
+    <t>routing and setup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref no </t>
   </si>
 </sst>
 </file>
@@ -564,7 +594,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -581,6 +611,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -917,7 +956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90D4E2F-31CB-4504-B764-69927272A7DB}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -944,30 +983,40 @@
       <c r="E1" s="4" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="F1" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
         <v>45931</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>43</v>
+      <c r="B2" s="8" t="s">
+        <v>158</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>44</v>
+        <v>159</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>45932</v>
+        <v>45931</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>153</v>
+        <v>44</v>
+      </c>
+      <c r="E3" s="4">
+        <v>3.1</v>
       </c>
       <c r="F3" s="4">
         <v>2</v>
@@ -975,197 +1024,212 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>45933</v>
+        <v>45932</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F4" s="4">
-        <v>3</v>
+      <c r="F4" s="8">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>45934</v>
+        <v>45933</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>153</v>
       </c>
       <c r="F5" s="4">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>45935</v>
+        <v>45934</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F6" s="4">
-        <v>5</v>
+      <c r="F6" s="8">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>45936</v>
+        <v>45935</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>153</v>
       </c>
       <c r="F7" s="4">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>45937</v>
+        <v>45936</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F8" s="4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="F8" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>45938</v>
+        <v>45937</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>153</v>
       </c>
       <c r="F9" s="4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>45939</v>
+        <v>45938</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F10" s="4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F10" s="8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>45940</v>
+        <v>45939</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>153</v>
       </c>
       <c r="F11" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>45941</v>
+        <v>45940</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F12" s="8">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>45942</v>
+        <v>45941</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="F13" s="4">
         <v>3</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>45943</v>
+        <v>45942</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
+      </c>
+      <c r="E14" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="F14" s="4">
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>45944</v>
+        <v>45943</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>63</v>
@@ -1174,571 +1238,757 @@
         <v>67</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
+      </c>
+      <c r="E15" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="F15" s="4">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>45945</v>
+        <v>45944</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>154</v>
+        <v>69</v>
+      </c>
+      <c r="E16" s="4">
+        <v>3.1</v>
       </c>
       <c r="F16" s="4">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>45946</v>
+        <v>45944</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>77</v>
+        <v>163</v>
+      </c>
+      <c r="E17" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="F17" s="4">
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>45947</v>
+        <v>45945</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F18" s="4">
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>45948</v>
+        <v>45946</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>45949</v>
+        <v>45947</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>45950</v>
+        <v>45948</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>45951</v>
+        <v>45949</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
+      </c>
+      <c r="E22" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="F22" s="4">
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>45952</v>
+        <v>45950</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
+      </c>
+      <c r="E23" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="F23" s="4">
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>45953</v>
+        <v>45951</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
+      </c>
+      <c r="E24" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="F24" s="4">
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>45954</v>
+        <v>45952</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
+      </c>
+      <c r="E25" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="F25" s="4">
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>45955</v>
+        <v>45953</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
+      </c>
+      <c r="E26" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="F26" s="4">
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>45956</v>
+        <v>45954</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
+      </c>
+      <c r="E27" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="F27" s="4">
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>45957</v>
+        <v>45955</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>154</v>
+        <v>95</v>
+      </c>
+      <c r="E28" s="4">
+        <v>3.1</v>
       </c>
       <c r="F28" s="4">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>45958</v>
+        <v>45956</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="F29" s="4">
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>45963</v>
+        <v>45957</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
+      </c>
+      <c r="E30" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="F30" s="4">
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>45971</v>
+        <v>45957</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>106</v>
+        <v>162</v>
+      </c>
+      <c r="E31" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="F31" s="4">
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
+        <v>45963</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>45971</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F33" s="4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
         <v>45973</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B34" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C34" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="5">
+      <c r="E34" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F34" s="4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
         <v>45993</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B35" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C35" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
+      <c r="E35" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F35" s="4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
         <v>45993</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B36" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C36" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F36" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>45993</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="5">
+      <c r="E37" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F37" s="4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
         <v>45996</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B38" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C38" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
+      <c r="E38" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F38" s="4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
         <v>45996</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C39" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="5">
+      <c r="E39" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F39" s="4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
         <v>45998</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B40" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="5">
+      <c r="E40" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F40" s="4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
         <v>45998</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B41" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C41" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="5">
+      <c r="E41" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F41" s="4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
         <v>45999</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B42" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C42" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="5">
+      <c r="E42" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F42" s="4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
         <v>45999</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B43" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C43" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="5">
+      <c r="E43" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F43" s="4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
         <v>46033</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B44" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C44" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="5">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
         <v>45677</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="5">
-        <v>46048</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="5">
-        <v>46053</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="5">
-        <v>46053</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>130</v>
       </c>
       <c r="C45" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>46048</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>46053</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D47" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>46053</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="5">
-        <v>46054</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="5">
-        <v>46054</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="5">
-        <v>46054</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
-        <v>46063</v>
+        <v>46054</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>148</v>
+      <c r="A50" s="5">
+        <v>46054</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <v>46063</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
         <v>46070</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B54" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C54" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>147</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{4EC61B37-2242-44D4-B428-A43BE3FF0C02}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{9B8160E2-44FB-4D13-AD78-3E845DE6EEA8}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{B077ABF8-90C3-4251-A7A8-CC5038A46452}"/>
-    <hyperlink ref="C4" r:id="rId4" location="Registerfields" xr:uid="{8EA72175-CAAD-4365-AB58-2B7428BA3E97}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{236BCE24-27DB-42C2-8C32-FE6EF3AC4B31}"/>
-    <hyperlink ref="C7" r:id="rId6" xr:uid="{F7569723-8CD7-46ED-B9CA-1D913EEC39A7}"/>
-    <hyperlink ref="C8" r:id="rId7" xr:uid="{6637D734-20BE-445B-A391-BD7F1B3213FF}"/>
-    <hyperlink ref="C9" r:id="rId8" xr:uid="{EBF4AA23-96D7-4AAB-BC6B-29E4C0B56188}"/>
-    <hyperlink ref="C10" r:id="rId9" xr:uid="{E12E5590-E8E0-4EA2-ABBC-66570FDB0EAF}"/>
-    <hyperlink ref="C12" r:id="rId10" xr:uid="{A30CE2FC-6D59-42BE-B8C1-C78BC442DB77}"/>
-    <hyperlink ref="C13" r:id="rId11" xr:uid="{E53C2B0D-EB91-4E0A-AB5D-BD5102965B28}"/>
-    <hyperlink ref="C14" r:id="rId12" xr:uid="{32B9C991-25C1-4C90-A7CB-F98B1355EC8C}"/>
-    <hyperlink ref="C15" r:id="rId13" xr:uid="{43648B55-640F-4FA0-B356-AB106B3CCF22}"/>
-    <hyperlink ref="C16" r:id="rId14" xr:uid="{FCEC304F-B202-4B79-BBA9-C6C6B1D93956}"/>
-    <hyperlink ref="C18" r:id="rId15" xr:uid="{398C7E09-D51E-48A9-ADF4-221657FABCA6}"/>
-    <hyperlink ref="C17" r:id="rId16" xr:uid="{CB4171ED-0F5B-4EC2-8BAF-5B3B33BB75E8}"/>
-    <hyperlink ref="C19" r:id="rId17" xr:uid="{A03C3256-87E0-46C8-98D4-D415943C42F9}"/>
-    <hyperlink ref="C20" r:id="rId18" xr:uid="{9F619F1F-BD6D-4C00-AA43-2D62F4C1E332}"/>
-    <hyperlink ref="C22" r:id="rId19" xr:uid="{DCA07648-473A-4D45-85F3-C816835BAD92}"/>
-    <hyperlink ref="C23" r:id="rId20" xr:uid="{65987E7D-4FC1-40A4-AB3E-A7526E37C4A3}"/>
-    <hyperlink ref="C24" r:id="rId21" xr:uid="{57A61951-44BF-4E6E-86E9-714912661AEB}"/>
-    <hyperlink ref="C21" r:id="rId22" xr:uid="{AB6498BE-D0BF-47CD-8622-0ED7994A1D21}"/>
-    <hyperlink ref="C25" r:id="rId23" xr:uid="{73DF6B83-C8E8-4552-AB90-977964502E8E}"/>
-    <hyperlink ref="C26" r:id="rId24" xr:uid="{14BA0721-63E0-4122-B951-344E6E827CE5}"/>
-    <hyperlink ref="C27" r:id="rId25" xr:uid="{B18FBBC8-C2F7-40AC-AECC-4065C837D233}"/>
-    <hyperlink ref="C28" r:id="rId26" xr:uid="{072DA101-1931-49E8-A980-D4E5DA46DA28}"/>
-    <hyperlink ref="C29" r:id="rId27" xr:uid="{175426E0-1FE8-40DB-BE91-6EC5C819E87C}"/>
-    <hyperlink ref="C30" r:id="rId28" xr:uid="{5A1495FF-2FD8-48B3-A242-89BA4C559C98}"/>
-    <hyperlink ref="C32" r:id="rId29" xr:uid="{F1C3C78B-B8E6-48A4-8F51-5148F47AE238}"/>
-    <hyperlink ref="C31" r:id="rId30" xr:uid="{7D53FE41-D04E-4CFD-855A-40B65B7655E2}"/>
-    <hyperlink ref="C33" r:id="rId31" xr:uid="{254DFCB9-A620-4255-A697-2CB786CA7CE3}"/>
-    <hyperlink ref="C35" r:id="rId32" xr:uid="{9199EC49-22AB-4322-AC33-4F2E57753EE3}"/>
-    <hyperlink ref="C36" r:id="rId33" xr:uid="{01609D78-3D3A-47F8-BF5A-5FF917290433}"/>
-    <hyperlink ref="C37" r:id="rId34" xr:uid="{3606DB42-0C27-49DA-ACF9-27FB2D79623A}"/>
-    <hyperlink ref="C34" r:id="rId35" xr:uid="{255A3E96-C2D8-4932-B7F1-72D2BB7D9B98}"/>
-    <hyperlink ref="C38" r:id="rId36" xr:uid="{0547D2F1-2A1F-4CE3-86EF-58E23F51E94A}"/>
-    <hyperlink ref="C39" r:id="rId37" xr:uid="{A68626F7-6347-4DAC-B7E4-420C7B476A2F}"/>
-    <hyperlink ref="C40" r:id="rId38" xr:uid="{CB9BD13E-9B50-44C5-82C4-024640EDF863}"/>
-    <hyperlink ref="C41" r:id="rId39" xr:uid="{816ECC41-1389-44F8-9A20-42011A9E6079}"/>
-    <hyperlink ref="C42" r:id="rId40" xr:uid="{2E2C1DD5-3948-43F7-B7A3-FE0B19F7DEEB}"/>
-    <hyperlink ref="C44" r:id="rId41" xr:uid="{6764F858-515A-4B83-9216-FFBFA8FCE642}"/>
-    <hyperlink ref="C45" r:id="rId42" xr:uid="{6E6DE7E9-364C-4FCC-A5DA-CBB159AD0435}"/>
-    <hyperlink ref="C43" r:id="rId43" xr:uid="{1C315DF0-53A6-45A6-A02F-95EC1F55D663}"/>
-    <hyperlink ref="C46" r:id="rId44" xr:uid="{D1A2AF0B-0CA2-407A-B6B1-EA7B73E18591}"/>
-    <hyperlink ref="C47" r:id="rId45" location="auth" xr:uid="{BC5DCA87-B939-4246-9E7B-C0D371B8B3B4}"/>
-    <hyperlink ref="C48" r:id="rId46" location="sending-credentials" xr:uid="{ABE0F341-2A39-4173-9F0A-66003E4641B7}"/>
-    <hyperlink ref="C49" r:id="rId47" xr:uid="{2E62C5DE-3858-4683-89AA-22F59BF60F30}"/>
-    <hyperlink ref="C51" r:id="rId48" xr:uid="{F155139A-3434-4782-B615-64B486D351D1}"/>
-    <hyperlink ref="C50" r:id="rId49" xr:uid="{76697DBB-3F51-4C18-B8A6-8E781AB753A0}"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{4EC61B37-2242-44D4-B428-A43BE3FF0C02}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{9B8160E2-44FB-4D13-AD78-3E845DE6EEA8}"/>
+    <hyperlink ref="C6" r:id="rId3" xr:uid="{B077ABF8-90C3-4251-A7A8-CC5038A46452}"/>
+    <hyperlink ref="C5" r:id="rId4" location="Registerfields" xr:uid="{8EA72175-CAAD-4365-AB58-2B7428BA3E97}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{236BCE24-27DB-42C2-8C32-FE6EF3AC4B31}"/>
+    <hyperlink ref="C8" r:id="rId6" xr:uid="{F7569723-8CD7-46ED-B9CA-1D913EEC39A7}"/>
+    <hyperlink ref="C9" r:id="rId7" xr:uid="{6637D734-20BE-445B-A391-BD7F1B3213FF}"/>
+    <hyperlink ref="C10" r:id="rId8" xr:uid="{EBF4AA23-96D7-4AAB-BC6B-29E4C0B56188}"/>
+    <hyperlink ref="C11" r:id="rId9" xr:uid="{E12E5590-E8E0-4EA2-ABBC-66570FDB0EAF}"/>
+    <hyperlink ref="C13" r:id="rId10" xr:uid="{A30CE2FC-6D59-42BE-B8C1-C78BC442DB77}"/>
+    <hyperlink ref="C14" r:id="rId11" xr:uid="{E53C2B0D-EB91-4E0A-AB5D-BD5102965B28}"/>
+    <hyperlink ref="C15" r:id="rId12" xr:uid="{32B9C991-25C1-4C90-A7CB-F98B1355EC8C}"/>
+    <hyperlink ref="C16" r:id="rId13" xr:uid="{43648B55-640F-4FA0-B356-AB106B3CCF22}"/>
+    <hyperlink ref="C18" r:id="rId14" xr:uid="{FCEC304F-B202-4B79-BBA9-C6C6B1D93956}"/>
+    <hyperlink ref="C20" r:id="rId15" xr:uid="{398C7E09-D51E-48A9-ADF4-221657FABCA6}"/>
+    <hyperlink ref="C19" r:id="rId16" xr:uid="{CB4171ED-0F5B-4EC2-8BAF-5B3B33BB75E8}"/>
+    <hyperlink ref="C21" r:id="rId17" xr:uid="{A03C3256-87E0-46C8-98D4-D415943C42F9}"/>
+    <hyperlink ref="C22" r:id="rId18" xr:uid="{9F619F1F-BD6D-4C00-AA43-2D62F4C1E332}"/>
+    <hyperlink ref="C24" r:id="rId19" xr:uid="{DCA07648-473A-4D45-85F3-C816835BAD92}"/>
+    <hyperlink ref="C25" r:id="rId20" xr:uid="{65987E7D-4FC1-40A4-AB3E-A7526E37C4A3}"/>
+    <hyperlink ref="C26" r:id="rId21" xr:uid="{57A61951-44BF-4E6E-86E9-714912661AEB}"/>
+    <hyperlink ref="C23" r:id="rId22" xr:uid="{AB6498BE-D0BF-47CD-8622-0ED7994A1D21}"/>
+    <hyperlink ref="C27" r:id="rId23" xr:uid="{73DF6B83-C8E8-4552-AB90-977964502E8E}"/>
+    <hyperlink ref="C28" r:id="rId24" xr:uid="{14BA0721-63E0-4122-B951-344E6E827CE5}"/>
+    <hyperlink ref="C29" r:id="rId25" xr:uid="{B18FBBC8-C2F7-40AC-AECC-4065C837D233}"/>
+    <hyperlink ref="C30" r:id="rId26" xr:uid="{072DA101-1931-49E8-A980-D4E5DA46DA28}"/>
+    <hyperlink ref="C17" r:id="rId27" xr:uid="{175426E0-1FE8-40DB-BE91-6EC5C819E87C}"/>
+    <hyperlink ref="C32" r:id="rId28" xr:uid="{5A1495FF-2FD8-48B3-A242-89BA4C559C98}"/>
+    <hyperlink ref="C34" r:id="rId29" xr:uid="{F1C3C78B-B8E6-48A4-8F51-5148F47AE238}"/>
+    <hyperlink ref="C33" r:id="rId30" xr:uid="{7D53FE41-D04E-4CFD-855A-40B65B7655E2}"/>
+    <hyperlink ref="C35" r:id="rId31" xr:uid="{254DFCB9-A620-4255-A697-2CB786CA7CE3}"/>
+    <hyperlink ref="C38" r:id="rId32" xr:uid="{9199EC49-22AB-4322-AC33-4F2E57753EE3}"/>
+    <hyperlink ref="C39" r:id="rId33" xr:uid="{01609D78-3D3A-47F8-BF5A-5FF917290433}"/>
+    <hyperlink ref="C40" r:id="rId34" xr:uid="{3606DB42-0C27-49DA-ACF9-27FB2D79623A}"/>
+    <hyperlink ref="C37" r:id="rId35" xr:uid="{255A3E96-C2D8-4932-B7F1-72D2BB7D9B98}"/>
+    <hyperlink ref="C41" r:id="rId36" xr:uid="{0547D2F1-2A1F-4CE3-86EF-58E23F51E94A}"/>
+    <hyperlink ref="C42" r:id="rId37" xr:uid="{A68626F7-6347-4DAC-B7E4-420C7B476A2F}"/>
+    <hyperlink ref="C43" r:id="rId38" xr:uid="{CB9BD13E-9B50-44C5-82C4-024640EDF863}"/>
+    <hyperlink ref="C44" r:id="rId39" xr:uid="{816ECC41-1389-44F8-9A20-42011A9E6079}"/>
+    <hyperlink ref="C45" r:id="rId40" xr:uid="{2E2C1DD5-3948-43F7-B7A3-FE0B19F7DEEB}"/>
+    <hyperlink ref="C47" r:id="rId41" xr:uid="{6764F858-515A-4B83-9216-FFBFA8FCE642}"/>
+    <hyperlink ref="C48" r:id="rId42" xr:uid="{6E6DE7E9-364C-4FCC-A5DA-CBB159AD0435}"/>
+    <hyperlink ref="C46" r:id="rId43" xr:uid="{1C315DF0-53A6-45A6-A02F-95EC1F55D663}"/>
+    <hyperlink ref="C49" r:id="rId44" xr:uid="{D1A2AF0B-0CA2-407A-B6B1-EA7B73E18591}"/>
+    <hyperlink ref="C50" r:id="rId45" location="auth" xr:uid="{BC5DCA87-B939-4246-9E7B-C0D371B8B3B4}"/>
+    <hyperlink ref="C51" r:id="rId46" location="sending-credentials" xr:uid="{ABE0F341-2A39-4173-9F0A-66003E4641B7}"/>
+    <hyperlink ref="C52" r:id="rId47" xr:uid="{2E62C5DE-3858-4683-89AA-22F59BF60F30}"/>
+    <hyperlink ref="C54" r:id="rId48" xr:uid="{F155139A-3434-4782-B615-64B486D351D1}"/>
+    <hyperlink ref="C53" r:id="rId49" xr:uid="{76697DBB-3F51-4C18-B8A6-8E781AB753A0}"/>
+    <hyperlink ref="C36" r:id="rId50" xr:uid="{AE3E5C53-ADCF-4F65-8074-6BF5F892939A}"/>
+    <hyperlink ref="C2" r:id="rId51" xr:uid="{5AB3A515-52DB-4C55-ABF4-499A818F05DB}"/>
+    <hyperlink ref="C31" r:id="rId52" xr:uid="{FDF38111-75A7-4BE4-AD7C-E239437BE1BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId50"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId53"/>
 </worksheet>
 </file>
 

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942E6BCB-826D-4D5A-8E37-C82D4CF9727D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64CBA12-9357-4C9B-8EC9-F00B6112B96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="165">
   <si>
     <t>Date</t>
   </si>
@@ -594,7 +594,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -611,15 +611,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -987,21 +978,20 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
         <v>45931</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="4" t="s">
         <v>158</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="8">
+      <c r="E2" s="4">
         <v>3.1</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="4">
         <v>1</v>
       </c>
     </row>
@@ -1035,7 +1025,7 @@
       <c r="E4" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="4">
         <v>18</v>
       </c>
     </row>
@@ -1069,7 +1059,7 @@
       <c r="E6" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="4">
         <v>20</v>
       </c>
     </row>
@@ -1103,7 +1093,7 @@
       <c r="E8" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="4">
         <v>22</v>
       </c>
     </row>
@@ -1143,7 +1133,7 @@
       <c r="E10" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="4">
         <v>24</v>
       </c>
     </row>
@@ -1183,7 +1173,7 @@
       <c r="E12" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="4">
         <v>26</v>
       </c>
     </row>
@@ -1795,6 +1785,12 @@
       </c>
       <c r="D44" s="3" t="s">
         <v>129</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F44" s="4">
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64CBA12-9357-4C9B-8EC9-F00B6112B96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C17C83-1FD8-4317-B7F5-707F31A74957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="166">
   <si>
     <t>Date</t>
   </si>
@@ -536,6 +536,9 @@
   </si>
   <si>
     <t xml:space="preserve">ref no </t>
+  </si>
+  <si>
+    <t>3.2.5</t>
   </si>
 </sst>
 </file>
@@ -1803,6 +1806,12 @@
       <c r="C45" s="6" t="s">
         <v>131</v>
       </c>
+      <c r="E45" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F45" s="4">
+        <v>39</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
@@ -1814,6 +1823,12 @@
       <c r="C46" s="6" t="s">
         <v>135</v>
       </c>
+      <c r="E46" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F46" s="4">
+        <v>40</v>
+      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
@@ -1828,6 +1843,12 @@
       <c r="D47" s="3" t="s">
         <v>134</v>
       </c>
+      <c r="E47" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F47" s="4">
+        <v>41</v>
+      </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
@@ -1842,8 +1863,14 @@
       <c r="D48" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F48" s="4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>46054</v>
       </c>
@@ -1856,8 +1883,14 @@
       <c r="D49" s="3" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F49" s="4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>46054</v>
       </c>
@@ -1870,8 +1903,14 @@
       <c r="D50" s="3" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F50" s="4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>46054</v>
       </c>
@@ -1884,8 +1923,14 @@
       <c r="D51" s="3" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F51" s="4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>46063</v>
       </c>
@@ -1898,8 +1943,14 @@
       <c r="D52" s="3" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E52" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F52" s="4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>148</v>
       </c>
@@ -1912,8 +1963,14 @@
       <c r="D53" s="3" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F53" s="4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>46070</v>
       </c>
@@ -1925,6 +1982,12 @@
       </c>
       <c r="D54" s="3" t="s">
         <v>147</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F54" s="4">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C17C83-1FD8-4317-B7F5-707F31A74957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D12A02-A3EA-4AAC-97F8-DFDF4DB149F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="169">
   <si>
     <t>Date</t>
   </si>
@@ -539,6 +539,15 @@
   </si>
   <si>
     <t>3.2.5</t>
+  </si>
+  <si>
+    <t>https://kitrum.com/blog/client-server-architecture-advantages-and-disadvantages/</t>
+  </si>
+  <si>
+    <t>https://www.geeksforgeeks.org/system-design/client-server-architecture-system-design/</t>
+  </si>
+  <si>
+    <t>https://medium.com/nerd-for-tech/client-server-architecture-explained-with-examples-diagrams-and-real-world-applications-407e9e04e2d1</t>
   </si>
 </sst>
 </file>
@@ -950,7 +959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90D4E2F-31CB-4504-B764-69927272A7DB}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -1988,6 +1997,21 @@
       </c>
       <c r="F54" s="4">
         <v>48</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C55" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C56" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C57" s="4" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D12A02-A3EA-4AAC-97F8-DFDF4DB149F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82539682-CFBF-4115-934D-BFA74536BB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="174">
   <si>
     <t>Date</t>
   </si>
@@ -548,6 +548,21 @@
   </si>
   <si>
     <t>https://medium.com/nerd-for-tech/client-server-architecture-explained-with-examples-diagrams-and-real-world-applications-407e9e04e2d1</t>
+  </si>
+  <si>
+    <t>ref for</t>
+  </si>
+  <si>
+    <t>user registration</t>
+  </si>
+  <si>
+    <t>tutor searching</t>
+  </si>
+  <si>
+    <t>lesson booking</t>
+  </si>
+  <si>
+    <t>real-time messaging</t>
   </si>
 </sst>
 </file>
@@ -959,7 +974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90D4E2F-31CB-4504-B764-69927272A7DB}">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -967,10 +982,12 @@
     <col min="3" max="3" width="92.140625" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="89.7109375" style="3" customWidth="1"/>
     <col min="5" max="5" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="4"/>
+    <col min="6" max="6" width="9.140625" style="4"/>
+    <col min="7" max="7" width="19.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -989,8 +1006,11 @@
       <c r="F1" s="4" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>45931</v>
       </c>
@@ -1007,7 +1027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>45931</v>
       </c>
@@ -1024,7 +1044,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>45932</v>
       </c>
@@ -1040,8 +1060,11 @@
       <c r="F4" s="4">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>45933</v>
       </c>
@@ -1057,8 +1080,11 @@
       <c r="F5" s="4">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>45934</v>
       </c>
@@ -1074,8 +1100,11 @@
       <c r="F6" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>45935</v>
       </c>
@@ -1091,8 +1120,11 @@
       <c r="F7" s="4">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>45936</v>
       </c>
@@ -1108,8 +1140,11 @@
       <c r="F8" s="4">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>45937</v>
       </c>
@@ -1128,8 +1163,11 @@
       <c r="F9" s="4">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="G9" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>45938</v>
       </c>
@@ -1148,8 +1186,11 @@
       <c r="F10" s="4">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G10" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>45939</v>
       </c>
@@ -1168,8 +1209,11 @@
       <c r="F11" s="4">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>45940</v>
       </c>
@@ -1188,8 +1232,11 @@
       <c r="F12" s="4">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>45941</v>
       </c>
@@ -1209,7 +1256,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>45942</v>
       </c>
@@ -1229,7 +1276,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>45943</v>
       </c>
@@ -1249,7 +1296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>45944</v>
       </c>
@@ -1565,7 +1612,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>45971</v>
       </c>
@@ -1584,8 +1631,11 @@
       <c r="F33" s="4">
         <v>27</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G33" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>45973</v>
       </c>
@@ -1604,8 +1654,11 @@
       <c r="F34" s="4">
         <v>28</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G34" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>45993</v>
       </c>
@@ -1624,8 +1677,11 @@
       <c r="F35" s="4">
         <v>29</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G35" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>45993</v>
       </c>
@@ -1644,8 +1700,11 @@
       <c r="F36" s="4">
         <v>30</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G36" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>45993</v>
       </c>
@@ -1664,8 +1723,11 @@
       <c r="F37" s="4">
         <v>31</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G37" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>45996</v>
       </c>
@@ -1684,8 +1746,11 @@
       <c r="F38" s="4">
         <v>32</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G38" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>45996</v>
       </c>
@@ -1704,8 +1769,11 @@
       <c r="F39" s="4">
         <v>33</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G39" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>45998</v>
       </c>
@@ -1724,8 +1792,11 @@
       <c r="F40" s="4">
         <v>34</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G40" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>45998</v>
       </c>
@@ -1744,8 +1815,11 @@
       <c r="F41" s="4">
         <v>35</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G41" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>45999</v>
       </c>
@@ -1764,8 +1838,11 @@
       <c r="F42" s="4">
         <v>36</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G42" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>45999</v>
       </c>
@@ -1784,8 +1861,11 @@
       <c r="F43" s="4">
         <v>37</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G43" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>46033</v>
       </c>
@@ -1804,8 +1884,11 @@
       <c r="F44" s="4">
         <v>38</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G44" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>45677</v>
       </c>
@@ -1821,8 +1904,11 @@
       <c r="F45" s="4">
         <v>39</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G45" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>46048</v>
       </c>
@@ -1838,8 +1924,11 @@
       <c r="F46" s="4">
         <v>40</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G46" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>46053</v>
       </c>
@@ -1858,8 +1947,11 @@
       <c r="F47" s="4">
         <v>41</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G47" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>46053</v>
       </c>
@@ -1878,8 +1970,11 @@
       <c r="F48" s="4">
         <v>42</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G48" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>46054</v>
       </c>
@@ -1898,8 +1993,11 @@
       <c r="F49" s="4">
         <v>43</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G49" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>46054</v>
       </c>
@@ -1918,8 +2016,11 @@
       <c r="F50" s="4">
         <v>44</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G50" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>46054</v>
       </c>
@@ -1938,8 +2039,11 @@
       <c r="F51" s="4">
         <v>45</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G51" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>46063</v>
       </c>
@@ -1958,8 +2062,11 @@
       <c r="F52" s="4">
         <v>46</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G52" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>148</v>
       </c>
@@ -1978,8 +2085,11 @@
       <c r="F53" s="4">
         <v>47</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G53" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>46070</v>
       </c>
@@ -1998,18 +2108,30 @@
       <c r="F54" s="4">
         <v>48</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G54" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
+        <v>46096</v>
+      </c>
       <c r="C55" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
+        <v>46096</v>
+      </c>
       <c r="C56" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="5">
+        <v>46096</v>
+      </c>
       <c r="C57" s="4" t="s">
         <v>168</v>
       </c>

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82539682-CFBF-4115-934D-BFA74536BB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB44EF62-3773-4DE6-B171-14005A4E8B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="178">
   <si>
     <t>Date</t>
   </si>
@@ -563,6 +563,18 @@
   </si>
   <si>
     <t>real-time messaging</t>
+  </si>
+  <si>
+    <t>zod on server</t>
+  </si>
+  <si>
+    <t>cosden solution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">webdev simplified </t>
+  </si>
+  <si>
+    <t>zod on server custom validation and handling errors</t>
   </si>
 </sst>
 </file>
@@ -974,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90D4E2F-31CB-4504-B764-69927272A7DB}">
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -2134,6 +2146,34 @@
       </c>
       <c r="C57" s="4" t="s">
         <v>168</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="5">
+        <v>46124</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>46124</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2191,9 +2231,11 @@
     <hyperlink ref="C36" r:id="rId50" xr:uid="{AE3E5C53-ADCF-4F65-8074-6BF5F892939A}"/>
     <hyperlink ref="C2" r:id="rId51" xr:uid="{5AB3A515-52DB-4C55-ABF4-499A818F05DB}"/>
     <hyperlink ref="C31" r:id="rId52" xr:uid="{FDF38111-75A7-4BE4-AD7C-E239437BE1BB}"/>
+    <hyperlink ref="C58" r:id="rId53" xr:uid="{4BCBB930-2600-4BD0-A0FF-9565BB17D6B7}"/>
+    <hyperlink ref="C59" r:id="rId54" xr:uid="{68912D8D-3E16-4512-951C-42E1A4EE1252}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId53"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId55"/>
 </worksheet>
 </file>
 

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB44EF62-3773-4DE6-B171-14005A4E8B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BDA364-725D-4BBB-A47E-56ADC62D6FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="181">
   <si>
     <t>Date</t>
   </si>
@@ -575,6 +575,15 @@
   </si>
   <si>
     <t>zod on server custom validation and handling errors</t>
+  </si>
+  <si>
+    <t>react router</t>
+  </si>
+  <si>
+    <t>navlink</t>
+  </si>
+  <si>
+    <t>NavLinkRenderProps</t>
   </si>
 </sst>
 </file>
@@ -986,7 +995,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90D4E2F-31CB-4504-B764-69927272A7DB}">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -2174,6 +2183,20 @@
       </c>
       <c r="D59" s="3" t="s">
         <v>177</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>46133</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2233,9 +2256,10 @@
     <hyperlink ref="C31" r:id="rId52" xr:uid="{FDF38111-75A7-4BE4-AD7C-E239437BE1BB}"/>
     <hyperlink ref="C58" r:id="rId53" xr:uid="{4BCBB930-2600-4BD0-A0FF-9565BB17D6B7}"/>
     <hyperlink ref="C59" r:id="rId54" xr:uid="{68912D8D-3E16-4512-951C-42E1A4EE1252}"/>
+    <hyperlink ref="C60" r:id="rId55" xr:uid="{E2B7A8BA-660B-4E6E-A449-BE8D06318890}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId55"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId56"/>
 </worksheet>
 </file>
 

--- a/docs/resource log.xlsx
+++ b/docs/resource log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\halog\Desktop\Music_Tutor_Project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BDA364-725D-4BBB-A47E-56ADC62D6FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E16CBFC-BFA5-41FC-B25B-B48AAB80C477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41780912-9485-457E-8E39-EF1EA0B82C48}"/>
   </bookViews>
@@ -517,9 +517,6 @@
     <t>basic walkthrough</t>
   </si>
   <si>
-    <t>react</t>
-  </si>
-  <si>
     <t>anson dev</t>
   </si>
   <si>
@@ -584,6 +581,9 @@
   </si>
   <si>
     <t>NavLinkRenderProps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">express  </t>
   </si>
 </sst>
 </file>
@@ -1025,10 +1025,10 @@
         <v>152</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1036,10 +1036,10 @@
         <v>45931</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="E2" s="4">
         <v>3.1</v>
@@ -1082,7 +1082,7 @@
         <v>18</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1102,7 +1102,7 @@
         <v>19</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1122,7 +1122,7 @@
         <v>20</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1142,7 +1142,7 @@
         <v>21</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1162,7 +1162,7 @@
         <v>22</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1185,7 +1185,7 @@
         <v>23</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="105" x14ac:dyDescent="0.25">
@@ -1208,7 +1208,7 @@
         <v>24</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1231,7 +1231,7 @@
         <v>25</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1254,7 +1254,7 @@
         <v>26</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1348,7 +1348,7 @@
         <v>101</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E17" s="4">
         <v>3.1</v>
@@ -1604,13 +1604,13 @@
         <v>45957</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="D31" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="E31" s="4">
         <v>3.1</v>
@@ -1653,7 +1653,7 @@
         <v>27</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -1676,7 +1676,7 @@
         <v>28</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -1699,7 +1699,7 @@
         <v>29</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1722,7 +1722,7 @@
         <v>30</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1745,7 +1745,7 @@
         <v>31</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1768,7 +1768,7 @@
         <v>32</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -1791,7 +1791,7 @@
         <v>33</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -1814,7 +1814,7 @@
         <v>34</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -1837,7 +1837,7 @@
         <v>35</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1860,7 +1860,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1883,7 +1883,7 @@
         <v>37</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1906,7 +1906,7 @@
         <v>38</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1920,13 +1920,13 @@
         <v>131</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F45" s="4">
         <v>39</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1940,13 +1940,13 @@
         <v>135</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F46" s="4">
         <v>40</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1963,13 +1963,13 @@
         <v>134</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F47" s="4">
         <v>41</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1986,13 +1986,13 @@
         <v>133</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F48" s="4">
         <v>42</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -2009,13 +2009,13 @@
         <v>138</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F49" s="4">
         <v>43</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2032,13 +2032,13 @@
         <v>140</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F50" s="4">
         <v>44</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -2055,13 +2055,13 @@
         <v>142</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F51" s="4">
         <v>45</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -2078,13 +2078,13 @@
         <v>145</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F52" s="4">
         <v>46</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -2101,13 +2101,13 @@
         <v>151</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F53" s="4">
         <v>47</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -2124,13 +2124,13 @@
         <v>147</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F54" s="4">
         <v>48</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -2138,7 +2138,7 @@
         <v>46096</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2146,7 +2146,7 @@
         <v>46096</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -2154,7 +2154,7 @@
         <v>46096</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -2162,13 +2162,13 @@
         <v>46124</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>175</v>
-      </c>
       <c r="D58" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -2176,13 +2176,13 @@
         <v>46124</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C59" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -2190,13 +2190,13 @@
         <v>46133</v>
       </c>
       <c r="B60" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="D60" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>180</v>
       </c>
     </row>
   </sheetData>
